--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-01-21T18:27:08.171Z</t>
+    <t>2026-01-21T21:44:32.954Z</t>
   </si>
   <si>
     <t>Fashion Blog</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-01-21T21:44:32.954Z</t>
+    <t>2026-01-21T21:48:54.124Z</t>
   </si>
   <si>
     <t>Fashion Blog</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["columns-hero","cards-features","cards-features","section-articles","cards-articles","section-tabs","tabs-showcase","section-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-cta"]</t>
+    <t>["columns-hero","cards-features","section-articles","cards-articles","section-tabs","tabs-showcase","section-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","columns-cta"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-01-21T21:48:54.124Z</t>
+    <t>2026-01-21T21:53:05.529Z</t>
   </si>
   <si>
     <t>Fashion Blog</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-02-05T16:38:54.924Z</t>
+    <t>2026-02-05T21:23:54.325Z</t>
   </si>
   <si>
     <t>Wireless Broadband for First Responders and Public Safety | FirstNet</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-02-05T21:23:54.325Z</t>
+    <t>2026-02-06T15:24:08.187Z</t>
   </si>
   <si>
     <t>Wireless Broadband for First Responders and Public Safety | FirstNet</t>
